--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128920885</v>
+        <v>128919341</v>
       </c>
       <c r="B2" t="n">
         <v>79739</v>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578712</v>
+        <v>578908</v>
       </c>
       <c r="R2" t="n">
-        <v>6341655</v>
+        <v>6341535</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128919341</v>
+        <v>128920885</v>
       </c>
       <c r="B3" t="n">
         <v>79739</v>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578908</v>
+        <v>578712</v>
       </c>
       <c r="R3" t="n">
-        <v>6341535</v>
+        <v>6341655</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1488,48 +1488,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128919463</v>
+        <v>128920961</v>
       </c>
       <c r="B10" t="n">
-        <v>91524</v>
+        <v>96228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578907</v>
+        <v>578797</v>
       </c>
       <c r="R10" t="n">
-        <v>6341582</v>
+        <v>6341536</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,7 +1595,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128918881</v>
+        <v>128919463</v>
       </c>
       <c r="B11" t="n">
         <v>91524</v>
@@ -1623,29 +1623,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578908</v>
+        <v>578907</v>
       </c>
       <c r="R11" t="n">
-        <v>6341535</v>
+        <v>6341582</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,9 +1663,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,60 +1690,69 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128920961</v>
+        <v>128918881</v>
       </c>
       <c r="B12" t="n">
-        <v>96228</v>
+        <v>91524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578797</v>
+        <v>578908</v>
       </c>
       <c r="R12" t="n">
-        <v>6341536</v>
+        <v>6341535</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1769,19 +1779,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,12 +1796,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128920205</v>
+        <v>128927695</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,42 +2115,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578827</v>
+        <v>578814</v>
       </c>
       <c r="R16" t="n">
-        <v>6341593</v>
+        <v>6341561</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,36 +2175,47 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927695</v>
+        <v>128927674</v>
       </c>
       <c r="B17" t="n">
         <v>79739</v>
@@ -2244,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578814</v>
+        <v>578789</v>
       </c>
       <c r="R17" t="n">
-        <v>6341561</v>
+        <v>6341540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128927674</v>
+        <v>128920205</v>
       </c>
       <c r="B18" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,40 +2337,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578789</v>
+        <v>578827</v>
       </c>
       <c r="R18" t="n">
-        <v>6341540</v>
+        <v>6341593</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,88 +2399,81 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128919941</v>
+        <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>79739</v>
+        <v>96228</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578917</v>
+        <v>578812</v>
       </c>
       <c r="R19" t="n">
-        <v>6341627</v>
+        <v>6341591</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2496,81 +2500,88 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128927540</v>
+        <v>128919941</v>
       </c>
       <c r="B20" t="n">
-        <v>96228</v>
+        <v>79739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578812</v>
+        <v>578917</v>
       </c>
       <c r="R20" t="n">
-        <v>6341591</v>
+        <v>6341627</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,40 +2608,29 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128920836</v>
+        <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>79739</v>
+        <v>96228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578760</v>
+        <v>578866</v>
       </c>
       <c r="R23" t="n">
-        <v>6341596</v>
+        <v>6341600</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128920087</v>
+        <v>128920836</v>
       </c>
       <c r="B24" t="n">
-        <v>96228</v>
+        <v>79739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578866</v>
+        <v>578760</v>
       </c>
       <c r="R24" t="n">
-        <v>6341600</v>
+        <v>6341596</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128919341</v>
       </c>
       <c r="B2" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128920885</v>
       </c>
       <c r="B3" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128919819</v>
       </c>
       <c r="B5" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128927635</v>
       </c>
       <c r="B6" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>128920977</v>
       </c>
       <c r="B7" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128920768</v>
       </c>
       <c r="B8" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128919953</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,48 +1488,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128920961</v>
+        <v>128919463</v>
       </c>
       <c r="B10" t="n">
-        <v>96228</v>
+        <v>91528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578797</v>
+        <v>578907</v>
       </c>
       <c r="R10" t="n">
-        <v>6341536</v>
+        <v>6341582</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128919463</v>
+        <v>128918881</v>
       </c>
       <c r="B11" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,20 +1623,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578907</v>
+        <v>578908</v>
       </c>
       <c r="R11" t="n">
-        <v>6341582</v>
+        <v>6341535</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,19 +1672,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1690,69 +1689,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128918881</v>
+        <v>128920961</v>
       </c>
       <c r="B12" t="n">
-        <v>91524</v>
+        <v>96232</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578908</v>
+        <v>578797</v>
       </c>
       <c r="R12" t="n">
-        <v>6341535</v>
+        <v>6341536</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1779,9 +1769,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,22 +1796,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920859</v>
+        <v>128920843</v>
       </c>
       <c r="B13" t="n">
-        <v>57713</v>
+        <v>79743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,42 +1819,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578715</v>
+        <v>578791</v>
       </c>
       <c r="R13" t="n">
-        <v>6341638</v>
+        <v>6341539</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,22 +1893,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920843</v>
+        <v>128920859</v>
       </c>
       <c r="B14" t="n">
-        <v>79739</v>
+        <v>57717</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1921,37 +1916,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578791</v>
+        <v>578715</v>
       </c>
       <c r="R14" t="n">
-        <v>6341539</v>
+        <v>6341638</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
         <v>128920910</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>128927695</v>
       </c>
       <c r="B16" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128927674</v>
       </c>
       <c r="B17" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>128920205</v>
       </c>
       <c r="B18" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>128919941</v>
       </c>
       <c r="B20" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128920948</v>
       </c>
       <c r="B22" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128920836</v>
       </c>
       <c r="B24" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>128927562</v>
       </c>
       <c r="B27" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1701,48 +1701,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128920961</v>
+        <v>128920859</v>
       </c>
       <c r="B12" t="n">
-        <v>96232</v>
+        <v>57717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578797</v>
+        <v>578715</v>
       </c>
       <c r="R12" t="n">
-        <v>6341536</v>
+        <v>6341638</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1769,19 +1774,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,60 +1791,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920843</v>
+        <v>128920961</v>
       </c>
       <c r="B13" t="n">
-        <v>79743</v>
+        <v>96232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578791</v>
+        <v>578797</v>
       </c>
       <c r="R13" t="n">
-        <v>6341539</v>
+        <v>6341536</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1876,9 +1871,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,22 +1898,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920859</v>
+        <v>128920843</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>79743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,42 +1921,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578715</v>
+        <v>578791</v>
       </c>
       <c r="R14" t="n">
-        <v>6341638</v>
+        <v>6341539</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3483,6 +3483,536 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128987559</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fliseryds-Boda 2.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>578577</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6341635</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128987533</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96232</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fliseryds-Boda 2.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>578645</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6341581</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128987545</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fliseryds-Boda 2.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>578607</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6341602</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128987493</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79743</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fliseryds-Boda 2.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>578787</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6341556</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128987483</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79743</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fliseryds-Boda 2.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>578815</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6341557</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128920859</v>
+        <v>128920843</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>79743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,42 +1712,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578715</v>
+        <v>578791</v>
       </c>
       <c r="R12" t="n">
-        <v>6341638</v>
+        <v>6341539</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1791,60 +1786,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920961</v>
+        <v>128920859</v>
       </c>
       <c r="B13" t="n">
-        <v>96232</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578797</v>
+        <v>578715</v>
       </c>
       <c r="R13" t="n">
-        <v>6341536</v>
+        <v>6341638</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,19 +1871,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,60 +1888,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920843</v>
+        <v>128920961</v>
       </c>
       <c r="B14" t="n">
-        <v>79743</v>
+        <v>96232</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578791</v>
+        <v>578797</v>
       </c>
       <c r="R14" t="n">
-        <v>6341539</v>
+        <v>6341536</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1978,9 +1968,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128919341</v>
       </c>
       <c r="B2" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128920885</v>
       </c>
       <c r="B3" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128919819</v>
       </c>
       <c r="B5" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128927635</v>
       </c>
       <c r="B6" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>128920977</v>
       </c>
       <c r="B7" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128920768</v>
       </c>
       <c r="B8" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128919953</v>
       </c>
       <c r="B9" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,48 +1488,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128919463</v>
+        <v>128920961</v>
       </c>
       <c r="B10" t="n">
-        <v>91528</v>
+        <v>96239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578907</v>
+        <v>578797</v>
       </c>
       <c r="R10" t="n">
-        <v>6341582</v>
+        <v>6341536</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128918881</v>
+        <v>128919463</v>
       </c>
       <c r="B11" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,29 +1623,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578908</v>
+        <v>578907</v>
       </c>
       <c r="R11" t="n">
-        <v>6341535</v>
+        <v>6341582</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,9 +1663,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,22 +1690,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128920843</v>
+        <v>128918881</v>
       </c>
       <c r="B12" t="n">
-        <v>79743</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,37 +1713,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578791</v>
+        <v>578908</v>
       </c>
       <c r="R12" t="n">
-        <v>6341539</v>
+        <v>6341535</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1786,22 +1796,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920859</v>
+        <v>128920843</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>79648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,42 +1819,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578715</v>
+        <v>578791</v>
       </c>
       <c r="R13" t="n">
-        <v>6341638</v>
+        <v>6341539</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1888,60 +1893,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920961</v>
+        <v>128920859</v>
       </c>
       <c r="B14" t="n">
-        <v>96232</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578797</v>
+        <v>578715</v>
       </c>
       <c r="R14" t="n">
-        <v>6341536</v>
+        <v>6341638</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1968,19 +1978,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
         <v>128920910</v>
       </c>
       <c r="B15" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128927695</v>
+        <v>128920205</v>
       </c>
       <c r="B16" t="n">
-        <v>79743</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,40 +2115,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578814</v>
+        <v>578827</v>
       </c>
       <c r="R16" t="n">
-        <v>6341561</v>
+        <v>6341593</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2175,50 +2177,39 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927674</v>
+        <v>128927695</v>
       </c>
       <c r="B17" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2253,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578789</v>
+        <v>578814</v>
       </c>
       <c r="R17" t="n">
-        <v>6341540</v>
+        <v>6341561</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2326,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128920205</v>
+        <v>128927674</v>
       </c>
       <c r="B18" t="n">
-        <v>57717</v>
+        <v>79648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,42 +2328,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578827</v>
+        <v>578789</v>
       </c>
       <c r="R18" t="n">
-        <v>6341593</v>
+        <v>6341540</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,29 +2388,40 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>128919941</v>
       </c>
       <c r="B20" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128920948</v>
       </c>
       <c r="B22" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128920836</v>
       </c>
       <c r="B24" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>128927562</v>
       </c>
       <c r="B27" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128987559</v>
       </c>
       <c r="B29" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>128987545</v>
       </c>
       <c r="B31" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128987493</v>
       </c>
       <c r="B32" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>128987483</v>
       </c>
       <c r="B33" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -869,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128920898</v>
+        <v>128919819</v>
       </c>
       <c r="B4" t="n">
-        <v>96247</v>
+        <v>79653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578780</v>
+        <v>578903</v>
       </c>
       <c r="R4" t="n">
-        <v>6341549</v>
+        <v>6341617</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -937,19 +937,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,60 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128919819</v>
+        <v>128920898</v>
       </c>
       <c r="B5" t="n">
-        <v>79653</v>
+        <v>96252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578903</v>
+        <v>578780</v>
       </c>
       <c r="R5" t="n">
-        <v>6341617</v>
+        <v>6341549</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,9 +1034,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,12 +1061,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1488,48 +1488,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128920961</v>
+        <v>128919463</v>
       </c>
       <c r="B10" t="n">
-        <v>96247</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578797</v>
+        <v>578907</v>
       </c>
       <c r="R10" t="n">
-        <v>6341536</v>
+        <v>6341582</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128920843</v>
+        <v>128918881</v>
       </c>
       <c r="B11" t="n">
-        <v>79653</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1606,37 +1606,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578791</v>
+        <v>578908</v>
       </c>
       <c r="R11" t="n">
-        <v>6341539</v>
+        <v>6341535</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,12 +1689,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1794,48 +1803,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128919463</v>
+        <v>128920961</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>96252</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578907</v>
+        <v>578797</v>
       </c>
       <c r="R13" t="n">
-        <v>6341582</v>
+        <v>6341536</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1864,7 +1873,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1874,7 +1883,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,10 +1910,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128918881</v>
+        <v>128920843</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>79653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1912,46 +1921,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578908</v>
+        <v>578791</v>
       </c>
       <c r="R14" t="n">
-        <v>6341535</v>
+        <v>6341539</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128927695</v>
+        <v>128920205</v>
       </c>
       <c r="B16" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,40 +2115,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578814</v>
+        <v>578827</v>
       </c>
       <c r="R16" t="n">
-        <v>6341561</v>
+        <v>6341593</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2175,47 +2177,36 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927674</v>
+        <v>128927695</v>
       </c>
       <c r="B17" t="n">
         <v>79653</v>
@@ -2253,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578789</v>
+        <v>578814</v>
       </c>
       <c r="R17" t="n">
-        <v>6341540</v>
+        <v>6341561</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2326,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128920205</v>
+        <v>128927674</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,42 +2328,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578827</v>
+        <v>578789</v>
       </c>
       <c r="R18" t="n">
-        <v>6341593</v>
+        <v>6341540</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,29 +2388,40 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927660</v>
+        <v>128927718</v>
       </c>
       <c r="B25" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578778</v>
+        <v>578818</v>
       </c>
       <c r="R25" t="n">
-        <v>6341547</v>
+        <v>6341566</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927718</v>
+        <v>128927660</v>
       </c>
       <c r="B26" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578818</v>
+        <v>578778</v>
       </c>
       <c r="R26" t="n">
-        <v>6341566</v>
+        <v>6341547</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128919341</v>
       </c>
       <c r="B2" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128920885</v>
       </c>
       <c r="B3" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128919819</v>
       </c>
       <c r="B4" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128920898</v>
       </c>
       <c r="B5" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128920768</v>
       </c>
       <c r="B8" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128919463</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>128918881</v>
       </c>
       <c r="B11" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,53 +1701,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128920859</v>
+        <v>128920961</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>96255</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578715</v>
+        <v>578797</v>
       </c>
       <c r="R12" t="n">
-        <v>6341638</v>
+        <v>6341536</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1774,9 +1769,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,60 +1796,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920961</v>
+        <v>128920843</v>
       </c>
       <c r="B13" t="n">
-        <v>96252</v>
+        <v>79654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578797</v>
+        <v>578791</v>
       </c>
       <c r="R13" t="n">
-        <v>6341536</v>
+        <v>6341539</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,19 +1876,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,22 +1893,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920843</v>
+        <v>128920859</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1921,37 +1916,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578791</v>
+        <v>578715</v>
       </c>
       <c r="R14" t="n">
-        <v>6341539</v>
+        <v>6341638</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
         <v>128920910</v>
       </c>
       <c r="B15" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128920205</v>
+        <v>128927695</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,42 +2115,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578827</v>
+        <v>578814</v>
       </c>
       <c r="R16" t="n">
-        <v>6341593</v>
+        <v>6341561</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,39 +2175,50 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927695</v>
+        <v>128927674</v>
       </c>
       <c r="B17" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2244,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578814</v>
+        <v>578789</v>
       </c>
       <c r="R17" t="n">
-        <v>6341561</v>
+        <v>6341540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128927674</v>
+        <v>128920205</v>
       </c>
       <c r="B18" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,40 +2337,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578789</v>
+        <v>578827</v>
       </c>
       <c r="R18" t="n">
-        <v>6341540</v>
+        <v>6341593</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,40 +2399,29 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>128919941</v>
       </c>
       <c r="B20" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128920948</v>
       </c>
       <c r="B22" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128920836</v>
       </c>
       <c r="B24" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927718</v>
+        <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578818</v>
+        <v>578778</v>
       </c>
       <c r="R25" t="n">
-        <v>6341566</v>
+        <v>6341547</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927660</v>
+        <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578778</v>
+        <v>578818</v>
       </c>
       <c r="R26" t="n">
-        <v>6341547</v>
+        <v>6341566</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128987493</v>
       </c>
       <c r="B32" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>128987483</v>
       </c>
       <c r="B33" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -869,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128919819</v>
+        <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>79654</v>
+        <v>96255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578903</v>
+        <v>578780</v>
       </c>
       <c r="R4" t="n">
-        <v>6341617</v>
+        <v>6341549</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -937,9 +937,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,60 +964,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128920898</v>
+        <v>128919819</v>
       </c>
       <c r="B5" t="n">
-        <v>96255</v>
+        <v>79654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578780</v>
+        <v>578903</v>
       </c>
       <c r="R5" t="n">
-        <v>6341549</v>
+        <v>6341617</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1034,19 +1044,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,12 +1061,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128919463</v>
+        <v>128920859</v>
       </c>
       <c r="B10" t="n">
-        <v>91546</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,37 +1499,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578907</v>
+        <v>578715</v>
       </c>
       <c r="R10" t="n">
-        <v>6341582</v>
+        <v>6341638</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1556,19 +1561,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,19 +1578,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128918881</v>
+        <v>128919463</v>
       </c>
       <c r="B11" t="n">
         <v>91546</v>
@@ -1623,29 +1618,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578908</v>
+        <v>578907</v>
       </c>
       <c r="R11" t="n">
-        <v>6341535</v>
+        <v>6341582</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,9 +1658,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,60 +1685,69 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128920961</v>
+        <v>128918881</v>
       </c>
       <c r="B12" t="n">
-        <v>96255</v>
+        <v>91546</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578797</v>
+        <v>578908</v>
       </c>
       <c r="R12" t="n">
-        <v>6341536</v>
+        <v>6341535</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1769,19 +1774,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,60 +1791,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920843</v>
+        <v>128920961</v>
       </c>
       <c r="B13" t="n">
-        <v>79654</v>
+        <v>96255</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578791</v>
+        <v>578797</v>
       </c>
       <c r="R13" t="n">
-        <v>6341539</v>
+        <v>6341536</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1876,9 +1871,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,22 +1898,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920859</v>
+        <v>128920843</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,42 +1921,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578715</v>
+        <v>578791</v>
       </c>
       <c r="R14" t="n">
-        <v>6341638</v>
+        <v>6341539</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128927695</v>
+        <v>128920205</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,40 +2115,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578814</v>
+        <v>578827</v>
       </c>
       <c r="R16" t="n">
-        <v>6341561</v>
+        <v>6341593</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2175,47 +2177,36 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927674</v>
+        <v>128927695</v>
       </c>
       <c r="B17" t="n">
         <v>79654</v>
@@ -2253,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578789</v>
+        <v>578814</v>
       </c>
       <c r="R17" t="n">
-        <v>6341540</v>
+        <v>6341561</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2326,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128920205</v>
+        <v>128927674</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,42 +2328,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578827</v>
+        <v>578789</v>
       </c>
       <c r="R18" t="n">
-        <v>6341593</v>
+        <v>6341540</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,29 +2388,40 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128920087</v>
+        <v>128920836</v>
       </c>
       <c r="B23" t="n">
-        <v>96255</v>
+        <v>79654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578866</v>
+        <v>578760</v>
       </c>
       <c r="R23" t="n">
-        <v>6341600</v>
+        <v>6341596</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128920836</v>
+        <v>128920087</v>
       </c>
       <c r="B24" t="n">
-        <v>79654</v>
+        <v>96255</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578760</v>
+        <v>578866</v>
       </c>
       <c r="R24" t="n">
-        <v>6341596</v>
+        <v>6341600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -869,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128920898</v>
+        <v>128919819</v>
       </c>
       <c r="B4" t="n">
-        <v>96255</v>
+        <v>79654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578780</v>
+        <v>578903</v>
       </c>
       <c r="R4" t="n">
-        <v>6341549</v>
+        <v>6341617</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -937,19 +937,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,60 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128919819</v>
+        <v>128920898</v>
       </c>
       <c r="B5" t="n">
-        <v>79654</v>
+        <v>96255</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578903</v>
+        <v>578780</v>
       </c>
       <c r="R5" t="n">
-        <v>6341617</v>
+        <v>6341549</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,9 +1034,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,12 +1061,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1488,53 +1488,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128920859</v>
+        <v>128920961</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>96255</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578715</v>
+        <v>578797</v>
       </c>
       <c r="R10" t="n">
-        <v>6341638</v>
+        <v>6341536</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,9 +1556,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,22 +1583,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128919463</v>
+        <v>128920843</v>
       </c>
       <c r="B11" t="n">
-        <v>91546</v>
+        <v>79654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,34 +1606,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578907</v>
+        <v>578791</v>
       </c>
       <c r="R11" t="n">
-        <v>6341582</v>
+        <v>6341539</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1658,19 +1663,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,19 +1680,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128918881</v>
+        <v>128919463</v>
       </c>
       <c r="B12" t="n">
         <v>91546</v>
@@ -1725,29 +1720,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578908</v>
+        <v>578907</v>
       </c>
       <c r="R12" t="n">
-        <v>6341535</v>
+        <v>6341582</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1774,9 +1760,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,60 +1787,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920961</v>
+        <v>128918881</v>
       </c>
       <c r="B13" t="n">
-        <v>96255</v>
+        <v>91546</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578797</v>
+        <v>578908</v>
       </c>
       <c r="R13" t="n">
-        <v>6341536</v>
+        <v>6341535</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,19 +1876,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,22 +1893,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920843</v>
+        <v>128920859</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1921,37 +1916,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578791</v>
+        <v>578715</v>
       </c>
       <c r="R14" t="n">
-        <v>6341539</v>
+        <v>6341638</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2428,52 +2428,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128927540</v>
+        <v>128919941</v>
       </c>
       <c r="B19" t="n">
-        <v>96255</v>
+        <v>79654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578812</v>
+        <v>578917</v>
       </c>
       <c r="R19" t="n">
-        <v>6341591</v>
+        <v>6341627</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2500,88 +2496,81 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128919941</v>
+        <v>128927540</v>
       </c>
       <c r="B20" t="n">
-        <v>79654</v>
+        <v>96255</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578917</v>
+        <v>578812</v>
       </c>
       <c r="R20" t="n">
-        <v>6341627</v>
+        <v>6341591</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2608,29 +2597,40 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128920836</v>
+        <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>79654</v>
+        <v>96255</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578760</v>
+        <v>578866</v>
       </c>
       <c r="R23" t="n">
-        <v>6341596</v>
+        <v>6341600</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128920087</v>
+        <v>128920836</v>
       </c>
       <c r="B24" t="n">
-        <v>96255</v>
+        <v>79654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578866</v>
+        <v>578760</v>
       </c>
       <c r="R24" t="n">
-        <v>6341600</v>
+        <v>6341596</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927660</v>
+        <v>128927718</v>
       </c>
       <c r="B25" t="n">
         <v>96255</v>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578778</v>
+        <v>578818</v>
       </c>
       <c r="R25" t="n">
-        <v>6341547</v>
+        <v>6341566</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927718</v>
+        <v>128927660</v>
       </c>
       <c r="B26" t="n">
         <v>96255</v>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578818</v>
+        <v>578778</v>
       </c>
       <c r="R26" t="n">
-        <v>6341566</v>
+        <v>6341547</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128919341</v>
       </c>
       <c r="B2" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128920885</v>
       </c>
       <c r="B3" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128919819</v>
+        <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>79654</v>
+        <v>96265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578903</v>
+        <v>578780</v>
       </c>
       <c r="R4" t="n">
-        <v>6341617</v>
+        <v>6341549</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -937,9 +937,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,60 +964,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128920898</v>
+        <v>128919819</v>
       </c>
       <c r="B5" t="n">
-        <v>96255</v>
+        <v>79658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578780</v>
+        <v>578903</v>
       </c>
       <c r="R5" t="n">
-        <v>6341549</v>
+        <v>6341617</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1034,19 +1044,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,12 +1061,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
         <v>128927635</v>
       </c>
       <c r="B6" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>128920977</v>
       </c>
       <c r="B7" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128920768</v>
       </c>
       <c r="B8" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128919953</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128920961</v>
       </c>
       <c r="B10" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>128920843</v>
       </c>
       <c r="B11" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128919463</v>
+        <v>128920859</v>
       </c>
       <c r="B12" t="n">
-        <v>91546</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,37 +1703,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578907</v>
+        <v>578715</v>
       </c>
       <c r="R12" t="n">
-        <v>6341582</v>
+        <v>6341638</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1760,19 +1765,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,22 +1782,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128918881</v>
+        <v>128919463</v>
       </c>
       <c r="B13" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,29 +1822,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578908</v>
+        <v>578907</v>
       </c>
       <c r="R13" t="n">
-        <v>6341535</v>
+        <v>6341582</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1876,9 +1862,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,22 +1889,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920859</v>
+        <v>128918881</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,42 +1912,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578715</v>
+        <v>578908</v>
       </c>
       <c r="R14" t="n">
-        <v>6341638</v>
+        <v>6341535</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>128920910</v>
       </c>
       <c r="B15" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128920205</v>
+        <v>128927695</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,42 +2115,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578827</v>
+        <v>578814</v>
       </c>
       <c r="R16" t="n">
-        <v>6341593</v>
+        <v>6341561</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,39 +2175,50 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927695</v>
+        <v>128927674</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2244,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578814</v>
+        <v>578789</v>
       </c>
       <c r="R17" t="n">
-        <v>6341561</v>
+        <v>6341540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128927674</v>
+        <v>128920205</v>
       </c>
       <c r="B18" t="n">
-        <v>79654</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,40 +2337,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578789</v>
+        <v>578827</v>
       </c>
       <c r="R18" t="n">
-        <v>6341540</v>
+        <v>6341593</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,40 +2399,29 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>128919941</v>
       </c>
       <c r="B19" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>128927540</v>
       </c>
       <c r="B20" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128920948</v>
       </c>
       <c r="B22" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128920836</v>
       </c>
       <c r="B24" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927718</v>
+        <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578818</v>
+        <v>578778</v>
       </c>
       <c r="R25" t="n">
-        <v>6341566</v>
+        <v>6341547</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927660</v>
+        <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578778</v>
+        <v>578818</v>
       </c>
       <c r="R26" t="n">
-        <v>6341547</v>
+        <v>6341566</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3262,7 +3262,7 @@
         <v>128927562</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128987559</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>128987545</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128987493</v>
       </c>
       <c r="B32" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>128987483</v>
       </c>
       <c r="B33" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2428,48 +2428,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128919941</v>
+        <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>79658</v>
+        <v>96265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578917</v>
+        <v>578812</v>
       </c>
       <c r="R19" t="n">
-        <v>6341627</v>
+        <v>6341591</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2496,81 +2500,88 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128927540</v>
+        <v>128919941</v>
       </c>
       <c r="B20" t="n">
-        <v>96265</v>
+        <v>79658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578812</v>
+        <v>578917</v>
       </c>
       <c r="R20" t="n">
-        <v>6341591</v>
+        <v>6341627</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,40 +2608,29 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -869,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128920898</v>
+        <v>128919819</v>
       </c>
       <c r="B4" t="n">
-        <v>96265</v>
+        <v>79658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578780</v>
+        <v>578903</v>
       </c>
       <c r="R4" t="n">
-        <v>6341549</v>
+        <v>6341617</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -937,19 +937,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,60 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128919819</v>
+        <v>128920898</v>
       </c>
       <c r="B5" t="n">
-        <v>79658</v>
+        <v>96272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578903</v>
+        <v>578780</v>
       </c>
       <c r="R5" t="n">
-        <v>6341617</v>
+        <v>6341549</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,9 +1034,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,12 +1061,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1488,48 +1488,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128920961</v>
+        <v>128920859</v>
       </c>
       <c r="B10" t="n">
-        <v>96265</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578797</v>
+        <v>578715</v>
       </c>
       <c r="R10" t="n">
-        <v>6341536</v>
+        <v>6341638</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1556,19 +1561,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,60 +1578,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128920843</v>
+        <v>128920961</v>
       </c>
       <c r="B11" t="n">
-        <v>79658</v>
+        <v>96272</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578791</v>
+        <v>578797</v>
       </c>
       <c r="R11" t="n">
-        <v>6341539</v>
+        <v>6341536</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,9 +1658,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,22 +1685,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128920859</v>
+        <v>128919463</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>91560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,42 +1708,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578715</v>
+        <v>578907</v>
       </c>
       <c r="R12" t="n">
-        <v>6341638</v>
+        <v>6341582</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,9 +1765,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,22 +1792,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128919463</v>
+        <v>128918881</v>
       </c>
       <c r="B13" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,20 +1832,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578907</v>
+        <v>578908</v>
       </c>
       <c r="R13" t="n">
-        <v>6341582</v>
+        <v>6341535</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1862,19 +1881,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,22 +1898,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128918881</v>
+        <v>128920843</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1912,46 +1921,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578908</v>
+        <v>578791</v>
       </c>
       <c r="R14" t="n">
-        <v>6341535</v>
+        <v>6341539</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128919341</v>
       </c>
       <c r="B2" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128920885</v>
       </c>
       <c r="B3" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128919819</v>
       </c>
       <c r="B4" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128920898</v>
       </c>
       <c r="B5" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128927635</v>
       </c>
       <c r="B6" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>128920977</v>
       </c>
       <c r="B7" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128920768</v>
       </c>
       <c r="B8" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128919953</v>
       </c>
       <c r="B9" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,53 +1488,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128920859</v>
+        <v>128920961</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>96274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578715</v>
+        <v>578797</v>
       </c>
       <c r="R10" t="n">
-        <v>6341638</v>
+        <v>6341536</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,9 +1556,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,60 +1583,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128920961</v>
+        <v>128918881</v>
       </c>
       <c r="B11" t="n">
-        <v>96272</v>
+        <v>91562</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578797</v>
+        <v>578908</v>
       </c>
       <c r="R11" t="n">
-        <v>6341536</v>
+        <v>6341535</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1658,19 +1672,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,12 +1689,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1700,7 +1704,7 @@
         <v>128919463</v>
       </c>
       <c r="B12" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128918881</v>
+        <v>128920843</v>
       </c>
       <c r="B13" t="n">
-        <v>91560</v>
+        <v>79660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1815,46 +1819,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578908</v>
+        <v>578791</v>
       </c>
       <c r="R13" t="n">
-        <v>6341535</v>
+        <v>6341539</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,22 +1893,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920843</v>
+        <v>128920859</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1921,37 +1916,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578791</v>
+        <v>578715</v>
       </c>
       <c r="R14" t="n">
-        <v>6341539</v>
+        <v>6341638</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
         <v>128920910</v>
       </c>
       <c r="B15" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>128927695</v>
       </c>
       <c r="B16" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128927674</v>
       </c>
       <c r="B17" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>128920205</v>
       </c>
       <c r="B18" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>128919941</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128920948</v>
       </c>
       <c r="B22" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128920087</v>
+        <v>128920836</v>
       </c>
       <c r="B23" t="n">
-        <v>96272</v>
+        <v>79660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578866</v>
+        <v>578760</v>
       </c>
       <c r="R23" t="n">
-        <v>6341600</v>
+        <v>6341596</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128920836</v>
+        <v>128920087</v>
       </c>
       <c r="B24" t="n">
-        <v>79658</v>
+        <v>96274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578760</v>
+        <v>578866</v>
       </c>
       <c r="R24" t="n">
-        <v>6341596</v>
+        <v>6341600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
         <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>128927562</v>
       </c>
       <c r="B27" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128987559</v>
       </c>
       <c r="B29" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>128987545</v>
       </c>
       <c r="B31" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128987493</v>
       </c>
       <c r="B32" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>128987483</v>
       </c>
       <c r="B33" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -1595,7 +1595,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128918881</v>
+        <v>128919463</v>
       </c>
       <c r="B11" t="n">
         <v>91562</v>
@@ -1623,29 +1623,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578908</v>
+        <v>578907</v>
       </c>
       <c r="R11" t="n">
-        <v>6341535</v>
+        <v>6341582</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,9 +1663,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,19 +1690,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128919463</v>
+        <v>128918881</v>
       </c>
       <c r="B12" t="n">
         <v>91562</v>
@@ -1729,20 +1730,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578907</v>
+        <v>578908</v>
       </c>
       <c r="R12" t="n">
-        <v>6341582</v>
+        <v>6341535</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1769,19 +1779,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,12 +1796,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128927695</v>
+        <v>128920205</v>
       </c>
       <c r="B16" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,40 +2115,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578814</v>
+        <v>578827</v>
       </c>
       <c r="R16" t="n">
-        <v>6341561</v>
+        <v>6341593</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2175,47 +2177,36 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927674</v>
+        <v>128927695</v>
       </c>
       <c r="B17" t="n">
         <v>79660</v>
@@ -2253,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578789</v>
+        <v>578814</v>
       </c>
       <c r="R17" t="n">
-        <v>6341540</v>
+        <v>6341561</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2326,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128920205</v>
+        <v>128927674</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,42 +2328,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578827</v>
+        <v>578789</v>
       </c>
       <c r="R18" t="n">
-        <v>6341593</v>
+        <v>6341540</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,29 +2388,40 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -869,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128919819</v>
+        <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>79660</v>
+        <v>96300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578903</v>
+        <v>578780</v>
       </c>
       <c r="R4" t="n">
-        <v>6341617</v>
+        <v>6341549</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -937,9 +937,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,60 +964,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128920898</v>
+        <v>128919819</v>
       </c>
       <c r="B5" t="n">
-        <v>96274</v>
+        <v>79660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578780</v>
+        <v>578903</v>
       </c>
       <c r="R5" t="n">
-        <v>6341549</v>
+        <v>6341617</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1034,19 +1044,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,12 +1061,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1491,7 +1491,7 @@
         <v>128920961</v>
       </c>
       <c r="B10" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>128919463</v>
       </c>
       <c r="B11" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128918881</v>
       </c>
       <c r="B12" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128920836</v>
+        <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>96300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578760</v>
+        <v>578866</v>
       </c>
       <c r="R23" t="n">
-        <v>6341596</v>
+        <v>6341600</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128920087</v>
+        <v>128920836</v>
       </c>
       <c r="B24" t="n">
-        <v>96274</v>
+        <v>79660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578866</v>
+        <v>578760</v>
       </c>
       <c r="R24" t="n">
-        <v>6341600</v>
+        <v>6341596</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927660</v>
+        <v>128927718</v>
       </c>
       <c r="B25" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578778</v>
+        <v>578818</v>
       </c>
       <c r="R25" t="n">
-        <v>6341547</v>
+        <v>6341566</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927718</v>
+        <v>128927660</v>
       </c>
       <c r="B26" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578818</v>
+        <v>578778</v>
       </c>
       <c r="R26" t="n">
-        <v>6341566</v>
+        <v>6341547</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128920961</v>
       </c>
       <c r="B10" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>128919463</v>
       </c>
       <c r="B11" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128918881</v>
       </c>
       <c r="B12" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920843</v>
+        <v>128920859</v>
       </c>
       <c r="B13" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,37 +1819,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578791</v>
+        <v>578715</v>
       </c>
       <c r="R13" t="n">
-        <v>6341539</v>
+        <v>6341638</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1893,22 +1898,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920859</v>
+        <v>128920843</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,42 +1921,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578715</v>
+        <v>578791</v>
       </c>
       <c r="R14" t="n">
-        <v>6341638</v>
+        <v>6341539</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927718</v>
+        <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578818</v>
+        <v>578778</v>
       </c>
       <c r="R25" t="n">
-        <v>6341566</v>
+        <v>6341547</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927660</v>
+        <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578778</v>
+        <v>578818</v>
       </c>
       <c r="R26" t="n">
-        <v>6341547</v>
+        <v>6341566</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1488,48 +1488,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128920961</v>
+        <v>128920843</v>
       </c>
       <c r="B10" t="n">
-        <v>96301</v>
+        <v>79660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578797</v>
+        <v>578791</v>
       </c>
       <c r="R10" t="n">
-        <v>6341536</v>
+        <v>6341539</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1556,19 +1556,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,19 +1573,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128919463</v>
+        <v>128918881</v>
       </c>
       <c r="B11" t="n">
         <v>91561</v>
@@ -1623,20 +1613,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578907</v>
+        <v>578908</v>
       </c>
       <c r="R11" t="n">
-        <v>6341582</v>
+        <v>6341535</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,19 +1662,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1690,19 +1679,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128918881</v>
+        <v>128919463</v>
       </c>
       <c r="B12" t="n">
         <v>91561</v>
@@ -1730,29 +1719,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578908</v>
+        <v>578907</v>
       </c>
       <c r="R12" t="n">
-        <v>6341535</v>
+        <v>6341582</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1779,9 +1759,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,12 +1786,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,48 +1900,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920843</v>
+        <v>128920961</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>96302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578791</v>
+        <v>578797</v>
       </c>
       <c r="R14" t="n">
-        <v>6341539</v>
+        <v>6341536</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1978,9 +1968,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2428,52 +2428,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128927540</v>
+        <v>128919941</v>
       </c>
       <c r="B19" t="n">
-        <v>96301</v>
+        <v>79660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578812</v>
+        <v>578917</v>
       </c>
       <c r="R19" t="n">
-        <v>6341591</v>
+        <v>6341627</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2500,88 +2496,81 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128919941</v>
+        <v>128927540</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>96302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578917</v>
+        <v>578812</v>
       </c>
       <c r="R20" t="n">
-        <v>6341627</v>
+        <v>6341591</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2608,29 +2597,40 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128919341</v>
       </c>
       <c r="B2" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128920885</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128919819</v>
       </c>
       <c r="B5" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128920768</v>
       </c>
       <c r="B8" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128920843</v>
+        <v>128919463</v>
       </c>
       <c r="B10" t="n">
-        <v>79660</v>
+        <v>91564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,34 +1499,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578791</v>
+        <v>578907</v>
       </c>
       <c r="R10" t="n">
-        <v>6341539</v>
+        <v>6341582</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1556,9 +1556,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,69 +1583,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128918881</v>
+        <v>128920961</v>
       </c>
       <c r="B11" t="n">
-        <v>91561</v>
+        <v>96306</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578908</v>
+        <v>578797</v>
       </c>
       <c r="R11" t="n">
-        <v>6341535</v>
+        <v>6341536</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1662,9 +1663,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1679,22 +1690,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128919463</v>
+        <v>128918881</v>
       </c>
       <c r="B12" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1719,20 +1730,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578907</v>
+        <v>578908</v>
       </c>
       <c r="R12" t="n">
-        <v>6341582</v>
+        <v>6341535</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1759,19 +1779,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,12 +1796,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1900,48 +1910,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920961</v>
+        <v>128920843</v>
       </c>
       <c r="B14" t="n">
-        <v>96302</v>
+        <v>79662</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578797</v>
+        <v>578791</v>
       </c>
       <c r="R14" t="n">
-        <v>6341536</v>
+        <v>6341539</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1968,19 +1978,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
         <v>128920910</v>
       </c>
       <c r="B15" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128920205</v>
+        <v>128927674</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>79662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,42 +2115,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578827</v>
+        <v>578789</v>
       </c>
       <c r="R16" t="n">
-        <v>6341593</v>
+        <v>6341540</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2177,39 +2175,50 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927695</v>
+        <v>128920205</v>
       </c>
       <c r="B17" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,40 +2226,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578814</v>
+        <v>578827</v>
       </c>
       <c r="R17" t="n">
-        <v>6341561</v>
+        <v>6341593</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2277,50 +2288,39 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128927674</v>
+        <v>128927695</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578789</v>
+        <v>578814</v>
       </c>
       <c r="R18" t="n">
-        <v>6341540</v>
+        <v>6341561</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2428,48 +2428,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128919941</v>
+        <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>79660</v>
+        <v>96306</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578917</v>
+        <v>578812</v>
       </c>
       <c r="R19" t="n">
-        <v>6341627</v>
+        <v>6341591</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2496,81 +2500,88 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128927540</v>
+        <v>128919941</v>
       </c>
       <c r="B20" t="n">
-        <v>96302</v>
+        <v>79662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578812</v>
+        <v>578917</v>
       </c>
       <c r="R20" t="n">
-        <v>6341591</v>
+        <v>6341627</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,40 +2608,29 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128920948</v>
       </c>
       <c r="B22" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>128920836</v>
       </c>
       <c r="B24" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128987493</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>128987483</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128919341</v>
       </c>
       <c r="B2" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128920885</v>
       </c>
       <c r="B3" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128919819</v>
       </c>
       <c r="B5" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128920768</v>
       </c>
       <c r="B8" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128919463</v>
       </c>
       <c r="B10" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,48 +1595,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128920961</v>
+        <v>128918881</v>
       </c>
       <c r="B11" t="n">
-        <v>96306</v>
+        <v>91566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578797</v>
+        <v>578908</v>
       </c>
       <c r="R11" t="n">
-        <v>6341536</v>
+        <v>6341535</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,19 +1672,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1690,22 +1689,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128918881</v>
+        <v>128920843</v>
       </c>
       <c r="B12" t="n">
-        <v>91564</v>
+        <v>79663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1713,46 +1712,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578908</v>
+        <v>578791</v>
       </c>
       <c r="R12" t="n">
-        <v>6341535</v>
+        <v>6341539</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,65 +1786,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920859</v>
+        <v>128920961</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>96308</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578715</v>
+        <v>578797</v>
       </c>
       <c r="R13" t="n">
-        <v>6341638</v>
+        <v>6341536</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1881,9 +1866,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,22 +1893,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920843</v>
+        <v>128920859</v>
       </c>
       <c r="B14" t="n">
-        <v>79662</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1921,37 +1916,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578791</v>
+        <v>578715</v>
       </c>
       <c r="R14" t="n">
-        <v>6341539</v>
+        <v>6341638</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,12 +1995,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
         <v>128920910</v>
       </c>
       <c r="B15" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128927674</v>
+        <v>128927695</v>
       </c>
       <c r="B16" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578789</v>
+        <v>578814</v>
       </c>
       <c r="R16" t="n">
-        <v>6341540</v>
+        <v>6341561</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128920205</v>
+        <v>128927674</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,42 +2226,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578827</v>
+        <v>578789</v>
       </c>
       <c r="R17" t="n">
-        <v>6341593</v>
+        <v>6341540</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2288,39 +2286,50 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128927695</v>
+        <v>128920205</v>
       </c>
       <c r="B18" t="n">
-        <v>79662</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,40 +2337,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578814</v>
+        <v>578827</v>
       </c>
       <c r="R18" t="n">
-        <v>6341561</v>
+        <v>6341593</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,40 +2399,29 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>128919941</v>
       </c>
       <c r="B20" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128920948</v>
       </c>
       <c r="B22" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128920087</v>
+        <v>128920836</v>
       </c>
       <c r="B23" t="n">
-        <v>96306</v>
+        <v>79663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578866</v>
+        <v>578760</v>
       </c>
       <c r="R23" t="n">
-        <v>6341600</v>
+        <v>6341596</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128920836</v>
+        <v>128920087</v>
       </c>
       <c r="B24" t="n">
-        <v>79662</v>
+        <v>96308</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578760</v>
+        <v>578866</v>
       </c>
       <c r="R24" t="n">
-        <v>6341596</v>
+        <v>6341600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
         <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>128987493</v>
       </c>
       <c r="B32" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>128987483</v>
       </c>
       <c r="B33" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128920898</v>
       </c>
       <c r="B4" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128919463</v>
       </c>
       <c r="B10" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>128918881</v>
       </c>
       <c r="B11" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,48 +1701,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128920843</v>
+        <v>128920961</v>
       </c>
       <c r="B12" t="n">
-        <v>79663</v>
+        <v>96312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578791</v>
+        <v>578797</v>
       </c>
       <c r="R12" t="n">
-        <v>6341539</v>
+        <v>6341536</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1769,9 +1769,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,60 +1796,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920961</v>
+        <v>128920843</v>
       </c>
       <c r="B13" t="n">
-        <v>96308</v>
+        <v>79663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578797</v>
+        <v>578791</v>
       </c>
       <c r="R13" t="n">
-        <v>6341536</v>
+        <v>6341539</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1866,19 +1876,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,12 +1893,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128927695</v>
+        <v>128920205</v>
       </c>
       <c r="B16" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,40 +2115,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578814</v>
+        <v>578827</v>
       </c>
       <c r="R16" t="n">
-        <v>6341561</v>
+        <v>6341593</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2175,47 +2177,36 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927674</v>
+        <v>128927695</v>
       </c>
       <c r="B17" t="n">
         <v>79663</v>
@@ -2253,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578789</v>
+        <v>578814</v>
       </c>
       <c r="R17" t="n">
-        <v>6341540</v>
+        <v>6341561</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2326,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128920205</v>
+        <v>128927674</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,42 +2328,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578827</v>
+        <v>578789</v>
       </c>
       <c r="R18" t="n">
-        <v>6341593</v>
+        <v>6341540</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,29 +2388,40 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>128927540</v>
       </c>
       <c r="B19" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>128920947</v>
       </c>
       <c r="B21" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128920836</v>
+        <v>128920087</v>
       </c>
       <c r="B23" t="n">
-        <v>79663</v>
+        <v>96312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578760</v>
+        <v>578866</v>
       </c>
       <c r="R23" t="n">
-        <v>6341596</v>
+        <v>6341600</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128920087</v>
+        <v>128920836</v>
       </c>
       <c r="B24" t="n">
-        <v>96308</v>
+        <v>79663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578866</v>
+        <v>578760</v>
       </c>
       <c r="R24" t="n">
-        <v>6341600</v>
+        <v>6341596</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
         <v>128927660</v>
       </c>
       <c r="B25" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>128927718</v>
       </c>
       <c r="B26" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128920686</v>
       </c>
       <c r="B28" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -3593,7 +3593,7 @@
         <v>128987533</v>
       </c>
       <c r="B30" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128919341</v>
+        <v>132737398</v>
       </c>
       <c r="B2" t="n">
-        <v>79663</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Smedrummossen, Smedrummossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578908</v>
+        <v>578562</v>
       </c>
       <c r="R2" t="n">
-        <v>6341535</v>
+        <v>6341720</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128920885</v>
+        <v>132737311</v>
       </c>
       <c r="B3" t="n">
-        <v>79663</v>
+        <v>92406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Smedrummossen, Smedrummossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578712</v>
+        <v>578562</v>
       </c>
       <c r="R3" t="n">
-        <v>6341655</v>
+        <v>6341720</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128920898</v>
+        <v>132737318</v>
       </c>
       <c r="B4" t="n">
-        <v>96312</v>
+        <v>92647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Smedrummossen, Smedrummossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578780</v>
+        <v>578562</v>
       </c>
       <c r="R4" t="n">
-        <v>6341549</v>
+        <v>6341720</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,44 +984,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128919819</v>
+        <v>128920087</v>
       </c>
       <c r="B5" t="n">
-        <v>79663</v>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578903</v>
+        <v>578866</v>
       </c>
       <c r="R5" t="n">
-        <v>6341617</v>
+        <v>6341600</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128927635</v>
+        <v>128920686</v>
       </c>
       <c r="B6" t="n">
-        <v>58097</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,49 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578684</v>
+        <v>578795</v>
       </c>
       <c r="R6" t="n">
-        <v>6341612</v>
+        <v>6341572</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1155,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1165,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128920977</v>
+        <v>128920898</v>
       </c>
       <c r="B7" t="n">
-        <v>58097</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,37 +1211,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578791</v>
+        <v>578780</v>
       </c>
       <c r="R7" t="n">
-        <v>6341539</v>
+        <v>6341549</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,9 +1268,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,60 +1295,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128920768</v>
+        <v>128920920</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578827</v>
+        <v>578780</v>
       </c>
       <c r="R8" t="n">
-        <v>6341593</v>
+        <v>6341550</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,9 +1375,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,65 +1402,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128919953</v>
+        <v>128920952</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578910</v>
+        <v>578797</v>
       </c>
       <c r="R9" t="n">
-        <v>6341608</v>
+        <v>6341536</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,9 +1482,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,60 +1509,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128919463</v>
+        <v>128927540</v>
       </c>
       <c r="B10" t="n">
-        <v>91570</v>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578907</v>
+        <v>578812</v>
       </c>
       <c r="R10" t="n">
-        <v>6341582</v>
+        <v>6341591</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,7 +1595,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1568,7 +1605,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1577,75 +1614,71 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128918881</v>
+        <v>128927660</v>
       </c>
       <c r="B11" t="n">
-        <v>91570</v>
+        <v>96708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578908</v>
+        <v>578778</v>
       </c>
       <c r="R11" t="n">
-        <v>6341535</v>
+        <v>6341547</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,39 +1705,50 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128920961</v>
+        <v>128927718</v>
       </c>
       <c r="B12" t="n">
-        <v>96312</v>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,19 +1774,23 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578797</v>
+        <v>578818</v>
       </c>
       <c r="R12" t="n">
-        <v>6341536</v>
+        <v>6341566</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,7 +1819,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1781,7 +1829,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,66 +1838,79 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920843</v>
+        <v>128987533</v>
       </c>
       <c r="B13" t="n">
-        <v>79663</v>
+        <v>96708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578791</v>
+        <v>578645</v>
       </c>
       <c r="R13" t="n">
-        <v>6341539</v>
+        <v>6341581</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,28 +1948,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128920859</v>
+        <v>128918881</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,42 +1978,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578715</v>
+        <v>578908</v>
       </c>
       <c r="R14" t="n">
-        <v>6341638</v>
+        <v>6341535</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2007,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128920910</v>
+        <v>128919463</v>
       </c>
       <c r="B15" t="n">
-        <v>78801</v>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2018,34 +2084,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578786</v>
+        <v>578907</v>
       </c>
       <c r="R15" t="n">
-        <v>6341549</v>
+        <v>6341582</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2075,9 +2141,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2092,22 +2168,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128920205</v>
+        <v>128920910</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,42 +2191,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578827</v>
+        <v>578786</v>
       </c>
       <c r="R16" t="n">
-        <v>6341593</v>
+        <v>6341549</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2194,22 +2265,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128927695</v>
+        <v>128920948</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,40 +2288,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578814</v>
+        <v>578790</v>
       </c>
       <c r="R17" t="n">
-        <v>6341561</v>
+        <v>6341547</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2277,50 +2345,39 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128927674</v>
+        <v>128919341</v>
       </c>
       <c r="B18" t="n">
-        <v>79663</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,22 +2403,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578789</v>
+        <v>578908</v>
       </c>
       <c r="R18" t="n">
-        <v>6341540</v>
+        <v>6341535</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,92 +2442,77 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128927540</v>
+        <v>128919819</v>
       </c>
       <c r="B19" t="n">
-        <v>96312</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578812</v>
+        <v>578903</v>
       </c>
       <c r="R19" t="n">
-        <v>6341591</v>
+        <v>6341617</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2500,40 +2539,29 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2543,7 +2571,7 @@
         <v>128919941</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,48 +2665,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128920947</v>
+        <v>128920768</v>
       </c>
       <c r="B21" t="n">
-        <v>96312</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578780</v>
+        <v>578827</v>
       </c>
       <c r="R21" t="n">
-        <v>6341550</v>
+        <v>6341593</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2705,19 +2733,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2732,22 +2750,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128920948</v>
+        <v>128920836</v>
       </c>
       <c r="B22" t="n">
-        <v>78801</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2755,37 +2773,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578790</v>
+        <v>578760</v>
       </c>
       <c r="R22" t="n">
-        <v>6341547</v>
+        <v>6341596</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2829,60 +2847,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128920087</v>
+        <v>128920843</v>
       </c>
       <c r="B23" t="n">
-        <v>96312</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578866</v>
+        <v>578791</v>
       </c>
       <c r="R23" t="n">
-        <v>6341600</v>
+        <v>6341539</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2926,22 +2944,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128920836</v>
+        <v>128920885</v>
       </c>
       <c r="B24" t="n">
-        <v>79663</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,13 +2991,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578760</v>
+        <v>578712</v>
       </c>
       <c r="R24" t="n">
-        <v>6341596</v>
+        <v>6341655</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3035,38 +3053,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927660</v>
+        <v>128927674</v>
       </c>
       <c r="B25" t="n">
-        <v>96312</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3074,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578778</v>
+        <v>578789</v>
       </c>
       <c r="R25" t="n">
-        <v>6341547</v>
+        <v>6341540</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3147,38 +3164,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927718</v>
+        <v>128927695</v>
       </c>
       <c r="B26" t="n">
-        <v>96312</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3186,10 +3202,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578818</v>
+        <v>578814</v>
       </c>
       <c r="R26" t="n">
-        <v>6341566</v>
+        <v>6341561</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3259,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927562</v>
+        <v>128987483</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3270,49 +3286,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578536</v>
+        <v>578815</v>
       </c>
       <c r="R27" t="n">
-        <v>6341648</v>
+        <v>6341557</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3339,87 +3350,85 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128920686</v>
+        <v>128987493</v>
       </c>
       <c r="B28" t="n">
-        <v>96312</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578795</v>
+        <v>578787</v>
       </c>
       <c r="R28" t="n">
-        <v>6341572</v>
+        <v>6341556</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3446,53 +3455,44 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128987559</v>
+        <v>128919687</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3514,21 +3514,18 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578577</v>
+        <v>578913</v>
       </c>
       <c r="R29" t="n">
         <v>6341635</v>
@@ -3590,10 +3587,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128987533</v>
+        <v>128919953</v>
       </c>
       <c r="B30" t="n">
-        <v>96320</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3601,49 +3598,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578645</v>
+        <v>578910</v>
       </c>
       <c r="R30" t="n">
-        <v>6341581</v>
+        <v>6341608</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3681,7 +3671,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3700,14 +3689,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128987545</v>
+        <v>128920205</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3729,27 +3718,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578607</v>
+        <v>578827</v>
       </c>
       <c r="R31" t="n">
-        <v>6341602</v>
+        <v>6341593</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3805,55 +3791,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128987493</v>
+        <v>128920859</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578787</v>
+        <v>578715</v>
       </c>
       <c r="R32" t="n">
-        <v>6341556</v>
+        <v>6341638</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3891,7 +3875,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3910,55 +3893,60 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128987483</v>
+        <v>128927562</v>
       </c>
       <c r="B33" t="n">
-        <v>79663</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578815</v>
+        <v>578536</v>
       </c>
       <c r="R33" t="n">
-        <v>6341557</v>
+        <v>6341648</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3985,75 +3973,92 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132737311</v>
+        <v>128987545</v>
       </c>
       <c r="B34" t="n">
-        <v>92378</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Smedrummossen, Smedrummossen, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578562</v>
+        <v>578607</v>
       </c>
       <c r="R34" t="n">
-        <v>6341720</v>
+        <v>6341602</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4080,22 +4085,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4110,65 +4105,68 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132741015</v>
+        <v>128987559</v>
       </c>
       <c r="B35" t="n">
-        <v>58119</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578930</v>
+        <v>578577</v>
       </c>
       <c r="R35" t="n">
-        <v>6341549</v>
+        <v>6341635</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4192,22 +4190,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4222,22 +4210,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132740648</v>
+        <v>128920974</v>
       </c>
       <c r="B36" t="n">
-        <v>5199</v>
+        <v>58327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4245,16 +4233,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4265,17 +4253,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578886</v>
+        <v>578791</v>
       </c>
       <c r="R36" t="n">
-        <v>6341561</v>
+        <v>6341539</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4299,22 +4287,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4329,60 +4307,72 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132737398</v>
+        <v>128927635</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>58327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Smedrummossen, Smedrummossen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578562</v>
+        <v>578684</v>
       </c>
       <c r="R37" t="n">
-        <v>6341720</v>
+        <v>6341612</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4406,22 +4396,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4436,60 +4426,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132737318</v>
+        <v>132741015</v>
       </c>
       <c r="B38" t="n">
-        <v>92573</v>
+        <v>58136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Smedrummossen, Smedrummossen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578562</v>
+        <v>578930</v>
       </c>
       <c r="R38" t="n">
-        <v>6341720</v>
+        <v>6341549</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4518,7 +4513,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4528,7 +4523,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4552,6 +4547,113 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132740648</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>578886</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6341561</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132737398</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132737311</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132737318</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920087</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920686</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920898</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920920</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920952</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128927540</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128927660</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128927718</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1964,6 +2024,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128987533</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2070,6 +2135,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918881</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2177,6 +2247,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128919463</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2274,6 +2349,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920910</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2371,6 +2451,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920948</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2468,6 +2553,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128919341</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2565,6 +2655,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128919819</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2662,6 +2757,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128919941</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2759,6 +2859,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920768</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2856,6 +2961,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920836</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2953,6 +3063,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920843</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3050,6 +3165,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920885</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3161,6 +3281,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128927674</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3272,6 +3397,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128927695</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3377,6 +3507,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128987483</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3482,6 +3617,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128987493</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3584,6 +3724,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128919687</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3686,6 +3831,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128919953</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3788,6 +3938,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920205</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3890,6 +4045,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920859</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4009,6 +4169,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128927562</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4114,6 +4279,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128987545</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4219,6 +4389,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128987559</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4316,6 +4491,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920974</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4435,6 +4615,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128927635</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4547,6 +4732,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132741015</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4654,8 +4844,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132740648</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>